--- a/03_Group_comparisons/Muscle_strength/c_data/01_design_contrasts.xlsx
+++ b/03_Group_comparisons/Muscle_strength/c_data/01_design_contrasts.xlsx
@@ -78,13 +78,13 @@
     <t>role</t>
   </si>
   <si>
-    <t>How the contrast is read: primary, secondary, descriptive, or floor (the baseline group difference).</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Feature level: proteins, sets or modules.</t>
+    <t>How the contrast is read: primary, secondary, descriptive, or baseline_reference (the baseline group difference).</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>What a correlation is estimated within.</t>
   </si>
   <si>
     <t>correlation</t>
@@ -129,55 +129,55 @@
     <t>Where the package came from.</t>
   </si>
   <si>
-    <t>Training_Hi = Hi_T2 - Hi_T1</t>
-  </si>
-  <si>
-    <t>Training_Hi</t>
+    <t>Training_HR = HR_T2 - HR_T1</t>
+  </si>
+  <si>
+    <t>Training_HR</t>
   </si>
   <si>
     <t>descriptive</t>
   </si>
   <si>
-    <t>Training_Lo = Lo_T2 - Lo_T1</t>
-  </si>
-  <si>
-    <t>Training_Lo</t>
-  </si>
-  <si>
-    <t>Acute_Hi = Hi_T3 - Hi_T2</t>
-  </si>
-  <si>
-    <t>Acute_Hi</t>
-  </si>
-  <si>
-    <t>Acute_Lo = Lo_T3 - Lo_T2</t>
-  </si>
-  <si>
-    <t>Acute_Lo</t>
-  </si>
-  <si>
-    <t>Baseline_HivLo = Hi_T1 - Lo_T1</t>
-  </si>
-  <si>
-    <t>Baseline_HivLo</t>
-  </si>
-  <si>
-    <t>floor</t>
-  </si>
-  <si>
-    <t>Trained_HivLo = Hi_T2 - Lo_T2</t>
-  </si>
-  <si>
-    <t>Trained_HivLo</t>
-  </si>
-  <si>
-    <t>Acute_HivLo = Hi_T3 - Lo_T3</t>
-  </si>
-  <si>
-    <t>Acute_HivLo</t>
-  </si>
-  <si>
-    <t>Training_Interaction = (Hi_T2 - Hi_T1) - (Lo_T2 - Lo_T1)</t>
+    <t>Training_LR = LR_T2 - LR_T1</t>
+  </si>
+  <si>
+    <t>Training_LR</t>
+  </si>
+  <si>
+    <t>Acute_HR = HR_T3 - HR_T2</t>
+  </si>
+  <si>
+    <t>Acute_HR</t>
+  </si>
+  <si>
+    <t>Acute_LR = LR_T3 - LR_T2</t>
+  </si>
+  <si>
+    <t>Acute_LR</t>
+  </si>
+  <si>
+    <t>Baseline_HRvLR = HR_T1 - LR_T1</t>
+  </si>
+  <si>
+    <t>Baseline_HRvLR</t>
+  </si>
+  <si>
+    <t>baseline_reference</t>
+  </si>
+  <si>
+    <t>Trained_HRvLR = HR_T2 - LR_T2</t>
+  </si>
+  <si>
+    <t>Trained_HRvLR</t>
+  </si>
+  <si>
+    <t>Acute_HRvLR = HR_T3 - LR_T3</t>
+  </si>
+  <si>
+    <t>Acute_HRvLR</t>
+  </si>
+  <si>
+    <t>Training_Interaction = (HR_T2 - HR_T1) - (LR_T2 - LR_T1)</t>
   </si>
   <si>
     <t>Training_Interaction</t>
@@ -186,7 +186,7 @@
     <t>primary</t>
   </si>
   <si>
-    <t>Acute_Interaction = (Hi_T3 - Hi_T2) - (Lo_T3 - Lo_T2)</t>
+    <t>Acute_Interaction = (HR_T3 - HR_T2) - (LR_T3 - LR_T2)</t>
   </si>
   <si>
     <t>Acute_Interaction</t>
@@ -204,7 +204,7 @@
     <t>01_Processing/03_Quantification/c_data/proteins.rds</t>
   </si>
   <si>
-    <t>34ef12f3ddbea70e6840925bab8692c5</t>
+    <t>765866aefeddf8c95296dd4824ecca44</t>
   </si>
   <si>
     <t>groups</t>
@@ -213,7 +213,7 @@
     <t>02_Groups/Muscle_strength/c_data/groups.rds</t>
   </si>
   <si>
-    <t>5bee9069ba18678f14ec2f9fe8fdc955</t>
+    <t>9c34d1b5902b27f6c2309b3fbbb7b009</t>
   </si>
   <si>
     <t>BiocGenerics</t>
